--- a/Data/Excel/mix-histology-duod.xlsx
+++ b/Data/Excel/mix-histology-duod.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28813"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cornellprod-my.sharepoint.com/personal/cjm423_cornell_edu/Documents/study-1-march25/MIX/Data/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1108" documentId="8_{8825706A-C66A-4F53-9E02-D5A3310D92F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39BAD614-E205-46B1-9784-07D0942F40CB}"/>
+  <xr:revisionPtr revIDLastSave="1469" documentId="8_{8825706A-C66A-4F53-9E02-D5A3310D92F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDA74A56-FD42-4AD6-A48C-529C79BCD305}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2C518FBD-9D68-4219-B0A2-9B67713B60FF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{2C518FBD-9D68-4219-B0A2-9B67713B60FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,12 +36,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>treatment</t>
-  </si>
-  <si>
-    <t>biological replicate</t>
   </si>
   <si>
     <t>villis_height</t>
@@ -62,17 +59,14 @@
     <t>goblet_count</t>
   </si>
   <si>
-    <t>NEUTRAL MAGENTA</t>
-  </si>
-  <si>
-    <t>ACID BLUE</t>
+    <t>biological_rep</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,6 +119,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -444,45 +442,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5E4AD02-2CBD-43F1-969A-A3AB7C967CD7}">
-  <dimension ref="A1:O351"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:H351"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="15">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="15">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -504,8 +502,11 @@
       <c r="G2">
         <v>12.55</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" ht="15">
+      <c r="H2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -527,8 +528,11 @@
       <c r="G3">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" ht="15">
+      <c r="H3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1</v>
       </c>
@@ -550,8 +554,11 @@
       <c r="G4">
         <v>14.47</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" ht="15">
+      <c r="H4">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1</v>
       </c>
@@ -573,8 +580,11 @@
       <c r="G5">
         <v>10.45</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" ht="15">
+      <c r="H5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1</v>
       </c>
@@ -596,8 +606,11 @@
       <c r="G6">
         <v>30.76</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" ht="15">
+      <c r="H6">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1</v>
       </c>
@@ -619,8 +632,11 @@
       <c r="G7">
         <v>10.39</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" ht="15">
+      <c r="H7">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1</v>
       </c>
@@ -642,11 +658,11 @@
       <c r="G8">
         <v>24.58</v>
       </c>
-      <c r="O8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="15">
+      <c r="H8">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>1</v>
       </c>
@@ -668,11 +684,11 @@
       <c r="G9">
         <v>22.66</v>
       </c>
-      <c r="O9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="15">
+      <c r="H9">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>1</v>
       </c>
@@ -694,8 +710,11 @@
       <c r="G10">
         <v>13.27</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" ht="15">
+      <c r="H10">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>1</v>
       </c>
@@ -717,8 +736,11 @@
       <c r="G11">
         <v>17.12</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" ht="15">
+      <c r="H11">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>1</v>
       </c>
@@ -740,8 +762,11 @@
       <c r="G12">
         <v>12.98</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" ht="15">
+      <c r="H12">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>1</v>
       </c>
@@ -763,8 +788,11 @@
       <c r="G13">
         <v>16.86</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" ht="15">
+      <c r="H13">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>1</v>
       </c>
@@ -786,8 +814,11 @@
       <c r="G14">
         <v>17.71</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" ht="15">
+      <c r="H14">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>1</v>
       </c>
@@ -809,8 +840,11 @@
       <c r="G15">
         <v>20.260000000000002</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" ht="15">
+      <c r="H15">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>1</v>
       </c>
@@ -832,8 +866,11 @@
       <c r="G16">
         <v>12.05</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="15">
+      <c r="H16">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>1</v>
       </c>
@@ -855,8 +892,11 @@
       <c r="G17">
         <v>21.67</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="15">
+      <c r="H17">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>1</v>
       </c>
@@ -878,8 +918,11 @@
       <c r="G18">
         <v>20.89</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="15">
+      <c r="H18">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>1</v>
       </c>
@@ -901,8 +944,11 @@
       <c r="G19">
         <v>19.579999999999998</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="15">
+      <c r="H19">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>1</v>
       </c>
@@ -924,8 +970,11 @@
       <c r="G20">
         <v>20.350000000000001</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" ht="15">
+      <c r="H20">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>1</v>
       </c>
@@ -947,8 +996,11 @@
       <c r="G21">
         <v>17.29</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="15">
+      <c r="H21">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>1</v>
       </c>
@@ -970,8 +1022,11 @@
       <c r="G22">
         <v>7.75</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" ht="15">
+      <c r="H22">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>1</v>
       </c>
@@ -993,8 +1048,11 @@
       <c r="G23">
         <v>17.75</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="15">
+      <c r="H23">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>1</v>
       </c>
@@ -1016,8 +1074,11 @@
       <c r="G24">
         <v>12.92</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="15">
+      <c r="H24">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>1</v>
       </c>
@@ -1039,8 +1100,11 @@
       <c r="G25">
         <v>15.13</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" ht="15">
+      <c r="H25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>1</v>
       </c>
@@ -1062,8 +1126,11 @@
       <c r="G26">
         <v>27.76</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" ht="15">
+      <c r="H26">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>1</v>
       </c>
@@ -1085,8 +1152,11 @@
       <c r="G27">
         <v>13.7</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" ht="15">
+      <c r="H27">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>1</v>
       </c>
@@ -1108,8 +1178,11 @@
       <c r="G28">
         <v>17.71</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="15">
+      <c r="H28">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>1</v>
       </c>
@@ -1131,8 +1204,11 @@
       <c r="G29">
         <v>16.97</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" ht="15">
+      <c r="H29">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>1</v>
       </c>
@@ -1154,8 +1230,11 @@
       <c r="G30">
         <v>17.190000000000001</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" ht="15">
+      <c r="H30">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>1</v>
       </c>
@@ -1177,8 +1256,11 @@
       <c r="G31">
         <v>15.91</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" ht="15">
+      <c r="H31">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>1</v>
       </c>
@@ -1200,8 +1282,11 @@
       <c r="G32">
         <v>10.39</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" ht="15">
+      <c r="H32">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>1</v>
       </c>
@@ -1223,8 +1308,11 @@
       <c r="G33">
         <v>13.33</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" ht="15">
+      <c r="H33">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>1</v>
       </c>
@@ -1246,8 +1334,11 @@
       <c r="G34">
         <v>9.48</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" ht="15">
+      <c r="H34">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>1</v>
       </c>
@@ -1269,8 +1360,11 @@
       <c r="G35">
         <v>12.21</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" ht="15">
+      <c r="H35">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>1</v>
       </c>
@@ -1292,8 +1386,11 @@
       <c r="G36">
         <v>17.12</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" ht="15">
+      <c r="H36">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>1</v>
       </c>
@@ -1315,8 +1412,11 @@
       <c r="G37">
         <v>13.65</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" ht="15">
+      <c r="H37">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>1</v>
       </c>
@@ -1338,8 +1438,11 @@
       <c r="G38">
         <v>17.809999999999999</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" ht="15">
+      <c r="H38">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>1</v>
       </c>
@@ -1361,8 +1464,11 @@
       <c r="G39">
         <v>23.27</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" ht="15">
+      <c r="H39">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>1</v>
       </c>
@@ -1384,8 +1490,11 @@
       <c r="G40">
         <v>16.61</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" ht="15">
+      <c r="H40">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>1</v>
       </c>
@@ -1407,8 +1516,11 @@
       <c r="G41">
         <v>12.22</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" ht="15">
+      <c r="H41">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>1</v>
       </c>
@@ -1430,8 +1542,11 @@
       <c r="G42">
         <v>12.96</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" ht="15">
+      <c r="H42">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>1</v>
       </c>
@@ -1453,8 +1568,11 @@
       <c r="G43">
         <v>20.77</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" ht="15">
+      <c r="H43">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>1</v>
       </c>
@@ -1476,8 +1594,11 @@
       <c r="G44">
         <v>8.43</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" ht="15">
+      <c r="H44">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>1</v>
       </c>
@@ -1499,8 +1620,11 @@
       <c r="G45">
         <v>13.7</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" ht="15">
+      <c r="H45">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>1</v>
       </c>
@@ -1522,8 +1646,11 @@
       <c r="G46">
         <v>17.21</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" ht="15">
+      <c r="H46">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>1</v>
       </c>
@@ -1545,8 +1672,11 @@
       <c r="G47">
         <v>14.21</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" ht="15">
+      <c r="H47">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>1</v>
       </c>
@@ -1568,8 +1698,11 @@
       <c r="G48">
         <v>14.06</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" ht="15">
+      <c r="H48">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>1</v>
       </c>
@@ -1591,8 +1724,11 @@
       <c r="G49">
         <v>14.58</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" ht="15">
+      <c r="H49">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>1</v>
       </c>
@@ -1614,8 +1750,11 @@
       <c r="G50">
         <v>14.41</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" ht="15">
+      <c r="H50">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>1</v>
       </c>
@@ -1637,8 +1776,11 @@
       <c r="G51">
         <v>11.44</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" ht="15">
+      <c r="H51">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>1</v>
       </c>
@@ -1660,8 +1802,11 @@
       <c r="G52">
         <v>14.78</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" ht="15">
+      <c r="H52">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>1</v>
       </c>
@@ -1683,8 +1828,11 @@
       <c r="G53">
         <v>21.52</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" ht="15">
+      <c r="H53">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>1</v>
       </c>
@@ -1706,8 +1854,11 @@
       <c r="G54">
         <v>15.44</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" ht="15">
+      <c r="H54">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>1</v>
       </c>
@@ -1729,8 +1880,11 @@
       <c r="G55">
         <v>22.14</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" ht="15">
+      <c r="H55">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>1</v>
       </c>
@@ -1752,8 +1906,11 @@
       <c r="G56">
         <v>15.95</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" ht="15">
+      <c r="H56">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>1</v>
       </c>
@@ -1775,8 +1932,11 @@
       <c r="G57">
         <v>10.9</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" ht="15">
+      <c r="H57">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>1</v>
       </c>
@@ -1798,8 +1958,11 @@
       <c r="G58">
         <v>17.54</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" ht="15">
+      <c r="H58">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>1</v>
       </c>
@@ -1821,8 +1984,11 @@
       <c r="G59">
         <v>8.61</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" ht="15">
+      <c r="H59">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>1</v>
       </c>
@@ -1844,8 +2010,11 @@
       <c r="G60">
         <v>19.5</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" ht="15">
+      <c r="H60">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>1</v>
       </c>
@@ -1867,8 +2036,11 @@
       <c r="G61">
         <v>17.54</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" ht="15">
+      <c r="H61">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>1</v>
       </c>
@@ -1890,8 +2062,11 @@
       <c r="G62">
         <v>13.92</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" ht="15">
+      <c r="H62">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>1</v>
       </c>
@@ -1913,8 +2088,11 @@
       <c r="G63">
         <v>8.89</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" ht="15">
+      <c r="H63">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>1</v>
       </c>
@@ -1936,8 +2114,11 @@
       <c r="G64">
         <v>10.99</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" ht="15">
+      <c r="H64">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>1</v>
       </c>
@@ -1959,8 +2140,11 @@
       <c r="G65">
         <v>11.17</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" ht="15">
+      <c r="H65">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>1</v>
       </c>
@@ -1982,8 +2166,11 @@
       <c r="G66">
         <v>14.7</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" ht="15">
+      <c r="H66">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>1</v>
       </c>
@@ -2005,8 +2192,11 @@
       <c r="G67">
         <v>11.67</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" ht="15">
+      <c r="H67">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>1</v>
       </c>
@@ -2028,8 +2218,11 @@
       <c r="G68">
         <v>22.73</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" ht="15">
+      <c r="H68">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>1</v>
       </c>
@@ -2051,8 +2244,11 @@
       <c r="G69">
         <v>12.22</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" ht="15">
+      <c r="H69">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>1</v>
       </c>
@@ -2074,8 +2270,11 @@
       <c r="G70">
         <v>12.01</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" ht="15">
+      <c r="H70">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>1</v>
       </c>
@@ -2097,8 +2296,11 @@
       <c r="G71">
         <v>21.72</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" ht="15">
+      <c r="H71">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>2</v>
       </c>
@@ -2120,8 +2322,11 @@
       <c r="G72">
         <v>11.41</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" ht="15">
+      <c r="H72">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>2</v>
       </c>
@@ -2143,8 +2348,11 @@
       <c r="G73">
         <v>11.11</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" ht="15">
+      <c r="H73">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>2</v>
       </c>
@@ -2166,8 +2374,11 @@
       <c r="G74">
         <v>19.260000000000002</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" ht="15">
+      <c r="H74">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>2</v>
       </c>
@@ -2189,8 +2400,11 @@
       <c r="G75">
         <v>33.869999999999997</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" ht="15">
+      <c r="H75">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>2</v>
       </c>
@@ -2212,8 +2426,11 @@
       <c r="G76">
         <v>6.19</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" ht="15">
+      <c r="H76">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>2</v>
       </c>
@@ -2235,8 +2452,11 @@
       <c r="G77">
         <v>8.69</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" ht="15">
+      <c r="H77">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>2</v>
       </c>
@@ -2258,8 +2478,11 @@
       <c r="G78">
         <v>10.5</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" ht="15">
+      <c r="H78">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>2</v>
       </c>
@@ -2281,8 +2504,11 @@
       <c r="G79">
         <v>8.06</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" ht="15">
+      <c r="H79">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>2</v>
       </c>
@@ -2304,8 +2530,11 @@
       <c r="G80">
         <v>10.039999999999999</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" ht="15">
+      <c r="H80">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>2</v>
       </c>
@@ -2327,8 +2556,11 @@
       <c r="G81">
         <v>17.36</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" ht="15">
+      <c r="H81">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>2</v>
       </c>
@@ -2350,8 +2582,11 @@
       <c r="G82">
         <v>8.41</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" ht="15">
+      <c r="H82">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>2</v>
       </c>
@@ -2373,8 +2608,11 @@
       <c r="G83">
         <v>11.67</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" ht="15">
+      <c r="H83">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>2</v>
       </c>
@@ -2396,8 +2634,11 @@
       <c r="G84">
         <v>14.94</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" ht="15">
+      <c r="H84">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>2</v>
       </c>
@@ -2419,8 +2660,11 @@
       <c r="G85">
         <v>9.39</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" ht="15">
+      <c r="H85">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>2</v>
       </c>
@@ -2442,8 +2686,11 @@
       <c r="G86">
         <v>11.53</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" ht="15">
+      <c r="H86">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>2</v>
       </c>
@@ -2465,8 +2712,11 @@
       <c r="G87">
         <v>15.85</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" ht="15">
+      <c r="H87">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>2</v>
       </c>
@@ -2488,8 +2738,11 @@
       <c r="G88">
         <v>10.49</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" ht="15">
+      <c r="H88">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>2</v>
       </c>
@@ -2511,8 +2764,11 @@
       <c r="G89">
         <v>9.9</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" ht="15">
+      <c r="H89">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>2</v>
       </c>
@@ -2534,8 +2790,11 @@
       <c r="G90">
         <v>10.97</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" ht="15">
+      <c r="H90">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>2</v>
       </c>
@@ -2557,8 +2816,11 @@
       <c r="G91">
         <v>8.41</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" ht="15">
+      <c r="H91">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>2</v>
       </c>
@@ -2572,7 +2834,7 @@
         <v>29.89</v>
       </c>
       <c r="E92">
-        <v>4531</v>
+        <v>45.31</v>
       </c>
       <c r="F92">
         <v>38.380000000000003</v>
@@ -2580,8 +2842,11 @@
       <c r="G92">
         <v>26.86</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" ht="15">
+      <c r="H92">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>2</v>
       </c>
@@ -2603,8 +2868,11 @@
       <c r="G93">
         <v>16.25</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" ht="15">
+      <c r="H93">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>2</v>
       </c>
@@ -2626,8 +2894,11 @@
       <c r="G94">
         <v>24.34</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" ht="15">
+      <c r="H94">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>2</v>
       </c>
@@ -2649,8 +2920,11 @@
       <c r="G95">
         <v>24.34</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" ht="15">
+      <c r="H95">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>2</v>
       </c>
@@ -2672,8 +2946,11 @@
       <c r="G96">
         <v>14.94</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" ht="15">
+      <c r="H96">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>2</v>
       </c>
@@ -2695,8 +2972,11 @@
       <c r="G97">
         <v>9.34</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" ht="15">
+      <c r="H97">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>2</v>
       </c>
@@ -2718,8 +2998,11 @@
       <c r="G98">
         <v>14.5</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" ht="15">
+      <c r="H98">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>2</v>
       </c>
@@ -2741,8 +3024,11 @@
       <c r="G99">
         <v>14.04</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" ht="15">
+      <c r="H99">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>2</v>
       </c>
@@ -2764,8 +3050,11 @@
       <c r="G100">
         <v>21.72</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" ht="15">
+      <c r="H100">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>2</v>
       </c>
@@ -2787,8 +3076,11 @@
       <c r="G101">
         <v>18.510000000000002</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" ht="15">
+      <c r="H101">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>2</v>
       </c>
@@ -2810,8 +3102,11 @@
       <c r="G102">
         <v>11.13</v>
       </c>
-    </row>
-    <row r="103" spans="1:7" ht="15">
+      <c r="H102">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>2</v>
       </c>
@@ -2833,8 +3128,11 @@
       <c r="G103">
         <v>12.96</v>
       </c>
-    </row>
-    <row r="104" spans="1:7" ht="15">
+      <c r="H103">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>2</v>
       </c>
@@ -2856,8 +3154,11 @@
       <c r="G104">
         <v>10.02</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" ht="15">
+      <c r="H104">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>2</v>
       </c>
@@ -2879,8 +3180,11 @@
       <c r="G105">
         <v>14.4</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" ht="15">
+      <c r="H105">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>2</v>
       </c>
@@ -2902,8 +3206,11 @@
       <c r="G106">
         <v>8.8699999999999992</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" ht="15">
+      <c r="H106">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>2</v>
       </c>
@@ -2925,8 +3232,11 @@
       <c r="G107">
         <v>16.86</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" ht="15">
+      <c r="H107">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>2</v>
       </c>
@@ -2948,8 +3258,11 @@
       <c r="G108">
         <v>9.75</v>
       </c>
-    </row>
-    <row r="109" spans="1:7" ht="15">
+      <c r="H108">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>2</v>
       </c>
@@ -2971,8 +3284,11 @@
       <c r="G109">
         <v>14.39</v>
       </c>
-    </row>
-    <row r="110" spans="1:7" ht="15">
+      <c r="H109">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>2</v>
       </c>
@@ -2994,8 +3310,11 @@
       <c r="G110">
         <v>12.23</v>
       </c>
-    </row>
-    <row r="111" spans="1:7" ht="15">
+      <c r="H110">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>2</v>
       </c>
@@ -3017,8 +3336,11 @@
       <c r="G111">
         <v>17.5</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" ht="15">
+      <c r="H111">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>2</v>
       </c>
@@ -3040,8 +3362,11 @@
       <c r="G112">
         <v>13.47</v>
       </c>
-    </row>
-    <row r="113" spans="1:7" ht="15">
+      <c r="H112">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>2</v>
       </c>
@@ -3063,8 +3388,11 @@
       <c r="G113">
         <v>9.9600000000000009</v>
       </c>
-    </row>
-    <row r="114" spans="1:7" ht="15">
+      <c r="H113">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>2</v>
       </c>
@@ -3086,8 +3414,11 @@
       <c r="G114">
         <v>26.21</v>
       </c>
-    </row>
-    <row r="115" spans="1:7" ht="15">
+      <c r="H114">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>2</v>
       </c>
@@ -3109,8 +3440,11 @@
       <c r="G115">
         <v>17.66</v>
       </c>
-    </row>
-    <row r="116" spans="1:7" ht="15">
+      <c r="H115">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>2</v>
       </c>
@@ -3132,8 +3466,11 @@
       <c r="G116">
         <v>7.43</v>
       </c>
-    </row>
-    <row r="117" spans="1:7" ht="15">
+      <c r="H116">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>2</v>
       </c>
@@ -3155,8 +3492,11 @@
       <c r="G117">
         <v>12.62</v>
       </c>
-    </row>
-    <row r="118" spans="1:7" ht="15">
+      <c r="H117">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>2</v>
       </c>
@@ -3178,8 +3518,11 @@
       <c r="G118">
         <v>16.46</v>
       </c>
-    </row>
-    <row r="119" spans="1:7" ht="15">
+      <c r="H118">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>2</v>
       </c>
@@ -3201,8 +3544,11 @@
       <c r="G119">
         <v>15.5</v>
       </c>
-    </row>
-    <row r="120" spans="1:7" ht="15">
+      <c r="H119">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>2</v>
       </c>
@@ -3224,8 +3570,11 @@
       <c r="G120">
         <v>20.309999999999999</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" ht="15">
+      <c r="H120">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>2</v>
       </c>
@@ -3247,8 +3596,11 @@
       <c r="G121">
         <v>10.9</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" ht="15">
+      <c r="H121">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>2</v>
       </c>
@@ -3270,8 +3622,11 @@
       <c r="G122">
         <v>19.82</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" ht="15">
+      <c r="H122">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>2</v>
       </c>
@@ -3293,8 +3648,11 @@
       <c r="G123">
         <v>11.97</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" ht="15">
+      <c r="H123">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>2</v>
       </c>
@@ -3316,8 +3674,11 @@
       <c r="G124">
         <v>10.5</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" ht="15">
+      <c r="H124">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>2</v>
       </c>
@@ -3339,8 +3700,11 @@
       <c r="G125">
         <v>20.8</v>
       </c>
-    </row>
-    <row r="126" spans="1:7" ht="15">
+      <c r="H125">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>2</v>
       </c>
@@ -3362,8 +3726,11 @@
       <c r="G126">
         <v>14.43</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" ht="15">
+      <c r="H126">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>2</v>
       </c>
@@ -3385,8 +3752,11 @@
       <c r="G127">
         <v>13.69</v>
       </c>
-    </row>
-    <row r="128" spans="1:7" ht="15">
+      <c r="H127">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>2</v>
       </c>
@@ -3408,8 +3778,11 @@
       <c r="G128">
         <v>15.28</v>
       </c>
-    </row>
-    <row r="129" spans="1:7" ht="15">
+      <c r="H128">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>2</v>
       </c>
@@ -3431,8 +3804,11 @@
       <c r="G129">
         <v>10.85</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" ht="15">
+      <c r="H129">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>2</v>
       </c>
@@ -3454,8 +3830,11 @@
       <c r="G130">
         <v>19.670000000000002</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" ht="15">
+      <c r="H130">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>2</v>
       </c>
@@ -3477,8 +3856,11 @@
       <c r="G131">
         <v>18.079999999999998</v>
       </c>
-    </row>
-    <row r="132" spans="1:7" ht="15">
+      <c r="H131">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>2</v>
       </c>
@@ -3500,8 +3882,11 @@
       <c r="G132">
         <v>14.43</v>
       </c>
-    </row>
-    <row r="133" spans="1:7" ht="15">
+      <c r="H132">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>2</v>
       </c>
@@ -3523,8 +3908,11 @@
       <c r="G133">
         <v>17.37</v>
       </c>
-    </row>
-    <row r="134" spans="1:7" ht="15">
+      <c r="H133">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>2</v>
       </c>
@@ -3546,8 +3934,11 @@
       <c r="G134">
         <v>14.8</v>
       </c>
-    </row>
-    <row r="135" spans="1:7" ht="15">
+      <c r="H134">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>2</v>
       </c>
@@ -3569,8 +3960,11 @@
       <c r="G135">
         <v>14.43</v>
       </c>
-    </row>
-    <row r="136" spans="1:7" ht="15">
+      <c r="H135">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>2</v>
       </c>
@@ -3592,8 +3986,11 @@
       <c r="G136">
         <v>12.62</v>
       </c>
-    </row>
-    <row r="137" spans="1:7" ht="15">
+      <c r="H136">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>2</v>
       </c>
@@ -3615,8 +4012,11 @@
       <c r="G137">
         <v>13.23</v>
       </c>
-    </row>
-    <row r="138" spans="1:7" ht="15">
+      <c r="H137">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>2</v>
       </c>
@@ -3638,8 +4038,11 @@
       <c r="G138">
         <v>19.22</v>
       </c>
-    </row>
-    <row r="139" spans="1:7" ht="15">
+      <c r="H138">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>2</v>
       </c>
@@ -3661,8 +4064,11 @@
       <c r="G139">
         <v>13.33</v>
       </c>
-    </row>
-    <row r="140" spans="1:7" ht="15">
+      <c r="H139">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>2</v>
       </c>
@@ -3684,8 +4090,11 @@
       <c r="G140">
         <v>24.88</v>
       </c>
-    </row>
-    <row r="141" spans="1:7" ht="15">
+      <c r="H140">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>2</v>
       </c>
@@ -3707,8 +4116,11 @@
       <c r="G141">
         <v>18.260000000000002</v>
       </c>
-    </row>
-    <row r="142" spans="1:7">
+      <c r="H141">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>7</v>
       </c>
@@ -3730,8 +4142,11 @@
       <c r="G142">
         <v>25.39</v>
       </c>
-    </row>
-    <row r="143" spans="1:7">
+      <c r="H142">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>7</v>
       </c>
@@ -3753,8 +4168,11 @@
       <c r="G143">
         <v>38.409999999999997</v>
       </c>
-    </row>
-    <row r="144" spans="1:7">
+      <c r="H143">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>7</v>
       </c>
@@ -3776,8 +4194,11 @@
       <c r="G144">
         <v>44.07</v>
       </c>
-    </row>
-    <row r="145" spans="1:7">
+      <c r="H144">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>7</v>
       </c>
@@ -3799,8 +4220,11 @@
       <c r="G145">
         <v>34.119999999999997</v>
       </c>
-    </row>
-    <row r="146" spans="1:7">
+      <c r="H145">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>7</v>
       </c>
@@ -3822,8 +4246,11 @@
       <c r="G146">
         <v>31.11</v>
       </c>
-    </row>
-    <row r="147" spans="1:7">
+      <c r="H146">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>7</v>
       </c>
@@ -3845,8 +4272,11 @@
       <c r="G147">
         <v>33</v>
       </c>
-    </row>
-    <row r="148" spans="1:7">
+      <c r="H147">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>7</v>
       </c>
@@ -3868,8 +4298,11 @@
       <c r="G148">
         <v>35.71</v>
       </c>
-    </row>
-    <row r="149" spans="1:7">
+      <c r="H148">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>7</v>
       </c>
@@ -3891,8 +4324,11 @@
       <c r="G149">
         <v>18.29</v>
       </c>
-    </row>
-    <row r="150" spans="1:7">
+      <c r="H149">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>7</v>
       </c>
@@ -3914,8 +4350,11 @@
       <c r="G150">
         <v>24.95</v>
       </c>
-    </row>
-    <row r="151" spans="1:7">
+      <c r="H150">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>7</v>
       </c>
@@ -3937,8 +4376,11 @@
       <c r="G151">
         <v>23.62</v>
       </c>
-    </row>
-    <row r="152" spans="1:7">
+      <c r="H151">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>7</v>
       </c>
@@ -3960,8 +4402,11 @@
       <c r="G152">
         <v>32.840000000000003</v>
       </c>
-    </row>
-    <row r="153" spans="1:7">
+      <c r="H152">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>7</v>
       </c>
@@ -3983,8 +4428,11 @@
       <c r="G153">
         <v>46.16</v>
       </c>
-    </row>
-    <row r="154" spans="1:7">
+      <c r="H153">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>7</v>
       </c>
@@ -4006,8 +4454,11 @@
       <c r="G154">
         <v>22.02</v>
       </c>
-    </row>
-    <row r="155" spans="1:7">
+      <c r="H154">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>7</v>
       </c>
@@ -4029,8 +4480,11 @@
       <c r="G155">
         <v>37.14</v>
       </c>
-    </row>
-    <row r="156" spans="1:7">
+      <c r="H155">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>7</v>
       </c>
@@ -4052,8 +4506,11 @@
       <c r="G156">
         <v>50.17</v>
       </c>
-    </row>
-    <row r="157" spans="1:7">
+      <c r="H156">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>7</v>
       </c>
@@ -4075,8 +4532,11 @@
       <c r="G157">
         <v>54.56</v>
       </c>
-    </row>
-    <row r="158" spans="1:7">
+      <c r="H157">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>7</v>
       </c>
@@ -4098,8 +4558,11 @@
       <c r="G158">
         <v>37.909999999999997</v>
       </c>
-    </row>
-    <row r="159" spans="1:7">
+      <c r="H158">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>7</v>
       </c>
@@ -4121,8 +4584,11 @@
       <c r="G159">
         <v>15.71</v>
       </c>
-    </row>
-    <row r="160" spans="1:7">
+      <c r="H159">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>7</v>
       </c>
@@ -4144,8 +4610,11 @@
       <c r="G160">
         <v>15.71</v>
       </c>
-    </row>
-    <row r="161" spans="1:7">
+      <c r="H160">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>7</v>
       </c>
@@ -4167,8 +4636,11 @@
       <c r="G161">
         <v>32.44</v>
       </c>
-    </row>
-    <row r="162" spans="1:7">
+      <c r="H161">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>7</v>
       </c>
@@ -4190,8 +4662,11 @@
       <c r="G162">
         <v>40.29</v>
       </c>
-    </row>
-    <row r="163" spans="1:7">
+      <c r="H162">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>7</v>
       </c>
@@ -4213,8 +4688,11 @@
       <c r="G163">
         <v>37.36</v>
       </c>
-    </row>
-    <row r="164" spans="1:7">
+      <c r="H163">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>7</v>
       </c>
@@ -4236,8 +4714,11 @@
       <c r="G164">
         <v>38.07</v>
       </c>
-    </row>
-    <row r="165" spans="1:7">
+      <c r="H164">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>7</v>
       </c>
@@ -4259,8 +4740,11 @@
       <c r="G165">
         <v>47.33</v>
       </c>
-    </row>
-    <row r="166" spans="1:7">
+      <c r="H165">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>7</v>
       </c>
@@ -4282,8 +4766,11 @@
       <c r="G166">
         <v>31.42</v>
       </c>
-    </row>
-    <row r="167" spans="1:7">
+      <c r="H166">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>7</v>
       </c>
@@ -4305,8 +4792,11 @@
       <c r="G167">
         <v>40.33</v>
       </c>
-    </row>
-    <row r="168" spans="1:7">
+      <c r="H167">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>7</v>
       </c>
@@ -4328,8 +4818,11 @@
       <c r="G168">
         <v>33.57</v>
       </c>
-    </row>
-    <row r="169" spans="1:7">
+      <c r="H168">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>7</v>
       </c>
@@ -4351,8 +4844,11 @@
       <c r="G169">
         <v>24.1</v>
       </c>
-    </row>
-    <row r="170" spans="1:7">
+      <c r="H169">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>7</v>
       </c>
@@ -4374,8 +4870,11 @@
       <c r="G170">
         <v>37.700000000000003</v>
       </c>
-    </row>
-    <row r="171" spans="1:7">
+      <c r="H170">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>7</v>
       </c>
@@ -4397,8 +4896,11 @@
       <c r="G171">
         <v>19.18</v>
       </c>
-    </row>
-    <row r="172" spans="1:7">
+      <c r="H171">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>7</v>
       </c>
@@ -4420,8 +4922,11 @@
       <c r="G172">
         <v>25.86</v>
       </c>
-    </row>
-    <row r="173" spans="1:7">
+      <c r="H172">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>7</v>
       </c>
@@ -4443,8 +4948,11 @@
       <c r="G173">
         <v>30.76</v>
       </c>
-    </row>
-    <row r="174" spans="1:7">
+      <c r="H173">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>7</v>
       </c>
@@ -4466,8 +4974,11 @@
       <c r="G174">
         <v>32.65</v>
       </c>
-    </row>
-    <row r="175" spans="1:7">
+      <c r="H174">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>7</v>
       </c>
@@ -4489,8 +5000,11 @@
       <c r="G175">
         <v>16.11</v>
       </c>
-    </row>
-    <row r="176" spans="1:7">
+      <c r="H175">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>7</v>
       </c>
@@ -4512,8 +5026,11 @@
       <c r="G176">
         <v>9.6199999999999992</v>
       </c>
-    </row>
-    <row r="177" spans="1:7">
+      <c r="H176">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>7</v>
       </c>
@@ -4535,8 +5052,11 @@
       <c r="G177">
         <v>31.45</v>
       </c>
-    </row>
-    <row r="178" spans="1:7">
+      <c r="H177">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>7</v>
       </c>
@@ -4558,8 +5078,11 @@
       <c r="G178">
         <v>9.59</v>
       </c>
-    </row>
-    <row r="179" spans="1:7">
+      <c r="H178">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>7</v>
       </c>
@@ -4581,8 +5104,11 @@
       <c r="G179">
         <v>17.440000000000001</v>
       </c>
-    </row>
-    <row r="180" spans="1:7">
+      <c r="H179">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>7</v>
       </c>
@@ -4604,8 +5130,11 @@
       <c r="G180">
         <v>26.04</v>
       </c>
-    </row>
-    <row r="181" spans="1:7">
+      <c r="H180">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>7</v>
       </c>
@@ -4627,8 +5156,11 @@
       <c r="G181">
         <v>18.45</v>
       </c>
-    </row>
-    <row r="182" spans="1:7">
+      <c r="H181">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>7</v>
       </c>
@@ -4650,8 +5182,11 @@
       <c r="G182">
         <v>40.840000000000003</v>
       </c>
-    </row>
-    <row r="183" spans="1:7">
+      <c r="H182">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>7</v>
       </c>
@@ -4673,8 +5208,11 @@
       <c r="G183">
         <v>26.51</v>
       </c>
-    </row>
-    <row r="184" spans="1:7">
+      <c r="H183">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>7</v>
       </c>
@@ -4696,8 +5234,11 @@
       <c r="G184">
         <v>21.2</v>
       </c>
-    </row>
-    <row r="185" spans="1:7">
+      <c r="H184">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>7</v>
       </c>
@@ -4719,8 +5260,11 @@
       <c r="G185">
         <v>24.68</v>
       </c>
-    </row>
-    <row r="186" spans="1:7">
+      <c r="H185">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>7</v>
       </c>
@@ -4742,8 +5286,11 @@
       <c r="G186">
         <v>25.1</v>
       </c>
-    </row>
-    <row r="187" spans="1:7">
+      <c r="H186">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>7</v>
       </c>
@@ -4765,8 +5312,11 @@
       <c r="G187">
         <v>16.12</v>
       </c>
-    </row>
-    <row r="188" spans="1:7">
+      <c r="H187">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>7</v>
       </c>
@@ -4788,8 +5338,11 @@
       <c r="G188">
         <v>22.45</v>
       </c>
-    </row>
-    <row r="189" spans="1:7">
+      <c r="H188">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>7</v>
       </c>
@@ -4811,8 +5364,11 @@
       <c r="G189">
         <v>32.85</v>
       </c>
-    </row>
-    <row r="190" spans="1:7">
+      <c r="H189">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>7</v>
       </c>
@@ -4834,8 +5390,11 @@
       <c r="G190">
         <v>26.95</v>
       </c>
-    </row>
-    <row r="191" spans="1:7">
+      <c r="H190">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>7</v>
       </c>
@@ -4857,8 +5416,11 @@
       <c r="G191">
         <v>24.9</v>
       </c>
-    </row>
-    <row r="192" spans="1:7">
+      <c r="H191">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>7</v>
       </c>
@@ -4880,8 +5442,11 @@
       <c r="G192">
         <v>29.97</v>
       </c>
-    </row>
-    <row r="193" spans="1:7">
+      <c r="H192">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>7</v>
       </c>
@@ -4903,8 +5468,11 @@
       <c r="G193">
         <v>19.36</v>
       </c>
-    </row>
-    <row r="194" spans="1:7">
+      <c r="H193">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>7</v>
       </c>
@@ -4926,8 +5494,11 @@
       <c r="G194">
         <v>31.23</v>
       </c>
-    </row>
-    <row r="195" spans="1:7">
+      <c r="H194">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>7</v>
       </c>
@@ -4949,8 +5520,11 @@
       <c r="G195">
         <v>41.87</v>
       </c>
-    </row>
-    <row r="196" spans="1:7">
+      <c r="H195">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>7</v>
       </c>
@@ -4972,8 +5546,11 @@
       <c r="G196">
         <v>31.72</v>
       </c>
-    </row>
-    <row r="197" spans="1:7">
+      <c r="H196">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>7</v>
       </c>
@@ -4995,8 +5572,11 @@
       <c r="G197">
         <v>35.03</v>
       </c>
-    </row>
-    <row r="198" spans="1:7">
+      <c r="H197">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>7</v>
       </c>
@@ -5018,8 +5598,11 @@
       <c r="G198">
         <v>35.81</v>
       </c>
-    </row>
-    <row r="199" spans="1:7">
+      <c r="H198">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>7</v>
       </c>
@@ -5041,8 +5624,11 @@
       <c r="G199">
         <v>29.54</v>
       </c>
-    </row>
-    <row r="200" spans="1:7">
+      <c r="H199">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>7</v>
       </c>
@@ -5064,8 +5650,11 @@
       <c r="G200">
         <v>30.72</v>
       </c>
-    </row>
-    <row r="201" spans="1:7">
+      <c r="H200">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>7</v>
       </c>
@@ -5087,8 +5676,11 @@
       <c r="G201">
         <v>27.14</v>
       </c>
-    </row>
-    <row r="202" spans="1:7">
+      <c r="H201">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A202">
         <v>7</v>
       </c>
@@ -5110,8 +5702,11 @@
       <c r="G202">
         <v>36.86</v>
       </c>
-    </row>
-    <row r="203" spans="1:7">
+      <c r="H202">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A203">
         <v>7</v>
       </c>
@@ -5133,8 +5728,11 @@
       <c r="G203">
         <v>20.11</v>
       </c>
-    </row>
-    <row r="204" spans="1:7">
+      <c r="H203">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>7</v>
       </c>
@@ -5156,8 +5754,11 @@
       <c r="G204">
         <v>22.3</v>
       </c>
-    </row>
-    <row r="205" spans="1:7">
+      <c r="H204">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>7</v>
       </c>
@@ -5179,8 +5780,11 @@
       <c r="G205">
         <v>51.96</v>
       </c>
-    </row>
-    <row r="206" spans="1:7">
+      <c r="H205">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>7</v>
       </c>
@@ -5202,8 +5806,11 @@
       <c r="G206">
         <v>35.96</v>
       </c>
-    </row>
-    <row r="207" spans="1:7">
+      <c r="H206">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>7</v>
       </c>
@@ -5225,8 +5832,11 @@
       <c r="G207">
         <v>51.45</v>
       </c>
-    </row>
-    <row r="208" spans="1:7">
+      <c r="H207">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A208">
         <v>7</v>
       </c>
@@ -5248,8 +5858,11 @@
       <c r="G208">
         <v>41.26</v>
       </c>
-    </row>
-    <row r="209" spans="1:7">
+      <c r="H208">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>7</v>
       </c>
@@ -5271,8 +5884,11 @@
       <c r="G209">
         <v>36.64</v>
       </c>
-    </row>
-    <row r="210" spans="1:7">
+      <c r="H209">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A210">
         <v>7</v>
       </c>
@@ -5294,8 +5910,11 @@
       <c r="G210">
         <v>40.369999999999997</v>
       </c>
-    </row>
-    <row r="211" spans="1:7">
+      <c r="H210">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>7</v>
       </c>
@@ -5317,8 +5936,11 @@
       <c r="G211">
         <v>20.82</v>
       </c>
-    </row>
-    <row r="212" spans="1:7">
+      <c r="H211">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A212">
         <v>8</v>
       </c>
@@ -5340,8 +5962,11 @@
       <c r="G212">
         <v>29.49</v>
       </c>
-    </row>
-    <row r="213" spans="1:7">
+      <c r="H212">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A213">
         <v>8</v>
       </c>
@@ -5363,8 +5988,11 @@
       <c r="G213">
         <v>42.76</v>
       </c>
-    </row>
-    <row r="214" spans="1:7">
+      <c r="H213">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A214">
         <v>8</v>
       </c>
@@ -5386,8 +6014,11 @@
       <c r="G214">
         <v>24.53</v>
       </c>
-    </row>
-    <row r="215" spans="1:7">
+      <c r="H214">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A215">
         <v>8</v>
       </c>
@@ -5409,8 +6040,11 @@
       <c r="G215">
         <v>28.15</v>
       </c>
-    </row>
-    <row r="216" spans="1:7">
+      <c r="H215">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>8</v>
       </c>
@@ -5432,8 +6066,11 @@
       <c r="G216">
         <v>25.12</v>
       </c>
-    </row>
-    <row r="217" spans="1:7">
+      <c r="H216">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A217">
         <v>8</v>
       </c>
@@ -5455,8 +6092,11 @@
       <c r="G217">
         <v>17.350000000000001</v>
       </c>
-    </row>
-    <row r="218" spans="1:7">
+      <c r="H217">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A218">
         <v>8</v>
       </c>
@@ -5478,8 +6118,11 @@
       <c r="G218">
         <v>25.78</v>
       </c>
-    </row>
-    <row r="219" spans="1:7">
+      <c r="H218">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A219">
         <v>8</v>
       </c>
@@ -5501,8 +6144,11 @@
       <c r="G219">
         <v>41.74</v>
       </c>
-    </row>
-    <row r="220" spans="1:7">
+      <c r="H219">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A220">
         <v>8</v>
       </c>
@@ -5524,8 +6170,11 @@
       <c r="G220">
         <v>14.02</v>
       </c>
-    </row>
-    <row r="221" spans="1:7">
+      <c r="H220">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A221">
         <v>8</v>
       </c>
@@ -5547,8 +6196,11 @@
       <c r="G221">
         <v>21.4</v>
       </c>
-    </row>
-    <row r="222" spans="1:7">
+      <c r="H221">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A222">
         <v>8</v>
       </c>
@@ -5570,8 +6222,11 @@
       <c r="G222">
         <v>18.63</v>
       </c>
-    </row>
-    <row r="223" spans="1:7">
+      <c r="H222">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A223">
         <v>8</v>
       </c>
@@ -5593,8 +6248,11 @@
       <c r="G223">
         <v>29.48</v>
       </c>
-    </row>
-    <row r="224" spans="1:7">
+      <c r="H223">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A224">
         <v>8</v>
       </c>
@@ -5616,8 +6274,11 @@
       <c r="G224">
         <v>38.18</v>
       </c>
-    </row>
-    <row r="225" spans="1:7">
+      <c r="H224">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>8</v>
       </c>
@@ -5639,8 +6300,11 @@
       <c r="G225">
         <v>22.07</v>
       </c>
-    </row>
-    <row r="226" spans="1:7">
+      <c r="H225">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A226">
         <v>8</v>
       </c>
@@ -5662,8 +6326,11 @@
       <c r="G226">
         <v>15.66</v>
       </c>
-    </row>
-    <row r="227" spans="1:7">
+      <c r="H226">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>8</v>
       </c>
@@ -5685,8 +6352,11 @@
       <c r="G227">
         <v>32.619999999999997</v>
       </c>
-    </row>
-    <row r="228" spans="1:7">
+      <c r="H227">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>8</v>
       </c>
@@ -5708,8 +6378,11 @@
       <c r="G228">
         <v>16.829999999999998</v>
       </c>
-    </row>
-    <row r="229" spans="1:7">
+      <c r="H228">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>8</v>
       </c>
@@ -5731,8 +6404,11 @@
       <c r="G229">
         <v>13.91</v>
       </c>
-    </row>
-    <row r="230" spans="1:7">
+      <c r="H229">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>8</v>
       </c>
@@ -5754,8 +6430,11 @@
       <c r="G230">
         <v>13.14</v>
       </c>
-    </row>
-    <row r="231" spans="1:7">
+      <c r="H230">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A231">
         <v>8</v>
       </c>
@@ -5777,8 +6456,11 @@
       <c r="G231">
         <v>13.3</v>
       </c>
-    </row>
-    <row r="232" spans="1:7">
+      <c r="H231">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A232">
         <v>8</v>
       </c>
@@ -5800,8 +6482,11 @@
       <c r="G232">
         <v>31.21</v>
       </c>
-    </row>
-    <row r="233" spans="1:7">
+      <c r="H232">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A233">
         <v>8</v>
       </c>
@@ -5823,8 +6508,11 @@
       <c r="G233">
         <v>44.83</v>
       </c>
-    </row>
-    <row r="234" spans="1:7">
+      <c r="H233">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A234">
         <v>8</v>
       </c>
@@ -5846,8 +6534,11 @@
       <c r="G234">
         <v>40.67</v>
       </c>
-    </row>
-    <row r="235" spans="1:7">
+      <c r="H234">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A235">
         <v>8</v>
       </c>
@@ -5869,8 +6560,11 @@
       <c r="G235">
         <v>30.26</v>
       </c>
-    </row>
-    <row r="236" spans="1:7">
+      <c r="H235">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A236">
         <v>8</v>
       </c>
@@ -5892,8 +6586,11 @@
       <c r="G236">
         <v>26.58</v>
       </c>
-    </row>
-    <row r="237" spans="1:7">
+      <c r="H236">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A237">
         <v>8</v>
       </c>
@@ -5915,8 +6612,11 @@
       <c r="G237">
         <v>12.1</v>
       </c>
-    </row>
-    <row r="238" spans="1:7">
+      <c r="H237">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A238">
         <v>8</v>
       </c>
@@ -5938,8 +6638,11 @@
       <c r="G238">
         <v>28.78</v>
       </c>
-    </row>
-    <row r="239" spans="1:7">
+      <c r="H238">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A239">
         <v>8</v>
       </c>
@@ -5961,8 +6664,11 @@
       <c r="G239">
         <v>14.84</v>
       </c>
-    </row>
-    <row r="240" spans="1:7">
+      <c r="H239">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A240">
         <v>8</v>
       </c>
@@ -5984,8 +6690,11 @@
       <c r="G240">
         <v>17.45</v>
       </c>
-    </row>
-    <row r="241" spans="1:7">
+      <c r="H240">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A241">
         <v>8</v>
       </c>
@@ -6007,8 +6716,11 @@
       <c r="G241">
         <v>36.97</v>
       </c>
-    </row>
-    <row r="242" spans="1:7">
+      <c r="H241">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A242">
         <v>8</v>
       </c>
@@ -6030,8 +6742,11 @@
       <c r="G242">
         <v>35.44</v>
       </c>
-    </row>
-    <row r="243" spans="1:7">
+      <c r="H242">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A243">
         <v>8</v>
       </c>
@@ -6053,8 +6768,11 @@
       <c r="G243">
         <v>17.670000000000002</v>
       </c>
-    </row>
-    <row r="244" spans="1:7">
+      <c r="H243">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A244">
         <v>8</v>
       </c>
@@ -6076,8 +6794,11 @@
       <c r="G244">
         <v>26.96</v>
       </c>
-    </row>
-    <row r="245" spans="1:7">
+      <c r="H244">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A245">
         <v>8</v>
       </c>
@@ -6099,8 +6820,11 @@
       <c r="G245">
         <v>15.85</v>
       </c>
-    </row>
-    <row r="246" spans="1:7">
+      <c r="H245">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A246">
         <v>8</v>
       </c>
@@ -6122,8 +6846,11 @@
       <c r="G246">
         <v>31.06</v>
       </c>
-    </row>
-    <row r="247" spans="1:7">
+      <c r="H246">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A247">
         <v>8</v>
       </c>
@@ -6145,8 +6872,11 @@
       <c r="G247">
         <v>36.07</v>
       </c>
-    </row>
-    <row r="248" spans="1:7">
+      <c r="H247">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A248">
         <v>8</v>
       </c>
@@ -6168,8 +6898,11 @@
       <c r="G248">
         <v>10.9</v>
       </c>
-    </row>
-    <row r="249" spans="1:7">
+      <c r="H248">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A249">
         <v>8</v>
       </c>
@@ -6191,8 +6924,11 @@
       <c r="G249">
         <v>12.33</v>
       </c>
-    </row>
-    <row r="250" spans="1:7">
+      <c r="H249">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A250">
         <v>8</v>
       </c>
@@ -6214,8 +6950,11 @@
       <c r="G250">
         <v>25.14</v>
       </c>
-    </row>
-    <row r="251" spans="1:7">
+      <c r="H250">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A251">
         <v>8</v>
       </c>
@@ -6237,8 +6976,11 @@
       <c r="G251">
         <v>11.09</v>
       </c>
-    </row>
-    <row r="252" spans="1:7">
+      <c r="H251">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A252">
         <v>8</v>
       </c>
@@ -6260,8 +7002,11 @@
       <c r="G252">
         <v>31.38</v>
       </c>
-    </row>
-    <row r="253" spans="1:7">
+      <c r="H252">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A253">
         <v>8</v>
       </c>
@@ -6283,8 +7028,11 @@
       <c r="G253">
         <v>50.74</v>
       </c>
-    </row>
-    <row r="254" spans="1:7">
+      <c r="H253">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A254">
         <v>8</v>
       </c>
@@ -6306,8 +7054,11 @@
       <c r="G254">
         <v>39.840000000000003</v>
       </c>
-    </row>
-    <row r="255" spans="1:7">
+      <c r="H254">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A255">
         <v>8</v>
       </c>
@@ -6329,8 +7080,11 @@
       <c r="G255">
         <v>27.92</v>
       </c>
-    </row>
-    <row r="256" spans="1:7">
+      <c r="H255">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A256">
         <v>8</v>
       </c>
@@ -6352,8 +7106,11 @@
       <c r="G256">
         <v>20.48</v>
       </c>
-    </row>
-    <row r="257" spans="1:7">
+      <c r="H256">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A257">
         <v>8</v>
       </c>
@@ -6375,8 +7132,11 @@
       <c r="G257">
         <v>25.06</v>
       </c>
-    </row>
-    <row r="258" spans="1:7">
+      <c r="H257">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A258">
         <v>8</v>
       </c>
@@ -6398,8 +7158,11 @@
       <c r="G258">
         <v>27.13</v>
       </c>
-    </row>
-    <row r="259" spans="1:7">
+      <c r="H258">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A259">
         <v>8</v>
       </c>
@@ -6421,8 +7184,11 @@
       <c r="G259">
         <v>39.229999999999997</v>
       </c>
-    </row>
-    <row r="260" spans="1:7">
+      <c r="H259">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A260">
         <v>8</v>
       </c>
@@ -6444,8 +7210,11 @@
       <c r="G260">
         <v>32.64</v>
       </c>
-    </row>
-    <row r="261" spans="1:7">
+      <c r="H260">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A261">
         <v>8</v>
       </c>
@@ -6467,8 +7236,11 @@
       <c r="G261">
         <v>23.14</v>
       </c>
-    </row>
-    <row r="262" spans="1:7">
+      <c r="H261">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A262">
         <v>8</v>
       </c>
@@ -6490,8 +7262,11 @@
       <c r="G262">
         <v>19.71</v>
       </c>
-    </row>
-    <row r="263" spans="1:7">
+      <c r="H262">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A263">
         <v>8</v>
       </c>
@@ -6513,8 +7288,11 @@
       <c r="G263">
         <v>16.39</v>
       </c>
-    </row>
-    <row r="264" spans="1:7">
+      <c r="H263">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A264">
         <v>8</v>
       </c>
@@ -6536,8 +7314,11 @@
       <c r="G264">
         <v>15.31</v>
       </c>
-    </row>
-    <row r="265" spans="1:7">
+      <c r="H264">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A265">
         <v>8</v>
       </c>
@@ -6559,8 +7340,11 @@
       <c r="G265">
         <v>11.49</v>
       </c>
-    </row>
-    <row r="266" spans="1:7">
+      <c r="H265">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A266">
         <v>8</v>
       </c>
@@ -6582,8 +7366,11 @@
       <c r="G266">
         <v>31</v>
       </c>
-    </row>
-    <row r="267" spans="1:7">
+      <c r="H266">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A267">
         <v>8</v>
       </c>
@@ -6605,8 +7392,11 @@
       <c r="G267">
         <v>13.53</v>
       </c>
-    </row>
-    <row r="268" spans="1:7">
+      <c r="H267">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A268">
         <v>8</v>
       </c>
@@ -6628,8 +7418,11 @@
       <c r="G268">
         <v>26.42</v>
       </c>
-    </row>
-    <row r="269" spans="1:7">
+      <c r="H268">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A269">
         <v>8</v>
       </c>
@@ -6651,8 +7444,11 @@
       <c r="G269">
         <v>13.61</v>
       </c>
-    </row>
-    <row r="270" spans="1:7">
+      <c r="H269">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A270">
         <v>8</v>
       </c>
@@ -6674,8 +7470,11 @@
       <c r="G270">
         <v>25.84</v>
       </c>
-    </row>
-    <row r="271" spans="1:7">
+      <c r="H270">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A271">
         <v>8</v>
       </c>
@@ -6697,8 +7496,11 @@
       <c r="G271">
         <v>19.71</v>
       </c>
-    </row>
-    <row r="272" spans="1:7">
+      <c r="H271">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A272">
         <v>8</v>
       </c>
@@ -6720,8 +7522,11 @@
       <c r="G272">
         <v>28.57</v>
       </c>
-    </row>
-    <row r="273" spans="1:7">
+      <c r="H272">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A273">
         <v>8</v>
       </c>
@@ -6743,8 +7548,11 @@
       <c r="G273">
         <v>24.12</v>
       </c>
-    </row>
-    <row r="274" spans="1:7">
+      <c r="H273">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A274">
         <v>8</v>
       </c>
@@ -6766,8 +7574,11 @@
       <c r="G274">
         <v>25.62</v>
       </c>
-    </row>
-    <row r="275" spans="1:7">
+      <c r="H274">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A275">
         <v>8</v>
       </c>
@@ -6789,8 +7600,11 @@
       <c r="G275">
         <v>38.28</v>
       </c>
-    </row>
-    <row r="276" spans="1:7">
+      <c r="H275">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A276">
         <v>8</v>
       </c>
@@ -6812,8 +7626,11 @@
       <c r="G276">
         <v>30.44</v>
       </c>
-    </row>
-    <row r="277" spans="1:7">
+      <c r="H276">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A277">
         <v>8</v>
       </c>
@@ -6835,8 +7652,11 @@
       <c r="G277">
         <v>17.190000000000001</v>
       </c>
-    </row>
-    <row r="278" spans="1:7">
+      <c r="H277">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A278">
         <v>8</v>
       </c>
@@ -6858,8 +7678,11 @@
       <c r="G278">
         <v>18.350000000000001</v>
       </c>
-    </row>
-    <row r="279" spans="1:7">
+      <c r="H278">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A279">
         <v>8</v>
       </c>
@@ -6881,8 +7704,11 @@
       <c r="G279">
         <v>20.69</v>
       </c>
-    </row>
-    <row r="280" spans="1:7">
+      <c r="H279">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A280">
         <v>8</v>
       </c>
@@ -6904,8 +7730,11 @@
       <c r="G280">
         <v>11.46</v>
       </c>
-    </row>
-    <row r="281" spans="1:7">
+      <c r="H280">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A281">
         <v>8</v>
       </c>
@@ -6927,8 +7756,11 @@
       <c r="G281">
         <v>16.34</v>
       </c>
-    </row>
-    <row r="282" spans="1:7">
+      <c r="H281">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A282">
         <v>9</v>
       </c>
@@ -6950,8 +7782,11 @@
       <c r="G282">
         <v>25.22</v>
       </c>
-    </row>
-    <row r="283" spans="1:7">
+      <c r="H282">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A283">
         <v>9</v>
       </c>
@@ -6973,8 +7808,11 @@
       <c r="G283">
         <v>40.770000000000003</v>
       </c>
-    </row>
-    <row r="284" spans="1:7">
+      <c r="H283">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A284">
         <v>9</v>
       </c>
@@ -6996,8 +7834,11 @@
       <c r="G284">
         <v>22.58</v>
       </c>
-    </row>
-    <row r="285" spans="1:7">
+      <c r="H284">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A285">
         <v>9</v>
       </c>
@@ -7019,8 +7860,11 @@
       <c r="G285">
         <v>44.74</v>
       </c>
-    </row>
-    <row r="286" spans="1:7">
+      <c r="H285">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A286">
         <v>9</v>
       </c>
@@ -7042,8 +7886,11 @@
       <c r="G286">
         <v>39.36</v>
       </c>
-    </row>
-    <row r="287" spans="1:7">
+      <c r="H286">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A287">
         <v>9</v>
       </c>
@@ -7065,8 +7912,11 @@
       <c r="G287">
         <v>29.45</v>
       </c>
-    </row>
-    <row r="288" spans="1:7">
+      <c r="H287">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A288">
         <v>9</v>
       </c>
@@ -7088,8 +7938,11 @@
       <c r="G288">
         <v>26.61</v>
       </c>
-    </row>
-    <row r="289" spans="1:7">
+      <c r="H288">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A289">
         <v>9</v>
       </c>
@@ -7111,8 +7964,11 @@
       <c r="G289">
         <v>27.97</v>
       </c>
-    </row>
-    <row r="290" spans="1:7">
+      <c r="H289">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A290">
         <v>9</v>
       </c>
@@ -7134,8 +7990,11 @@
       <c r="G290">
         <v>28.47</v>
       </c>
-    </row>
-    <row r="291" spans="1:7">
+      <c r="H290">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A291">
         <v>9</v>
       </c>
@@ -7157,8 +8016,11 @@
       <c r="G291">
         <v>36.07</v>
       </c>
-    </row>
-    <row r="292" spans="1:7">
+      <c r="H291">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A292">
         <v>9</v>
       </c>
@@ -7180,8 +8042,11 @@
       <c r="G292">
         <v>21.45</v>
       </c>
-    </row>
-    <row r="293" spans="1:7">
+      <c r="H292">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A293">
         <v>9</v>
       </c>
@@ -7203,8 +8068,11 @@
       <c r="G293">
         <v>19.559999999999999</v>
       </c>
-    </row>
-    <row r="294" spans="1:7">
+      <c r="H293">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A294">
         <v>9</v>
       </c>
@@ -7226,8 +8094,11 @@
       <c r="G294">
         <v>30.82</v>
       </c>
-    </row>
-    <row r="295" spans="1:7">
+      <c r="H294">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A295">
         <v>9</v>
       </c>
@@ -7249,8 +8120,11 @@
       <c r="G295">
         <v>24.15</v>
       </c>
-    </row>
-    <row r="296" spans="1:7">
+      <c r="H295">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A296">
         <v>9</v>
       </c>
@@ -7272,8 +8146,11 @@
       <c r="G296">
         <v>27.66</v>
       </c>
-    </row>
-    <row r="297" spans="1:7">
+      <c r="H296">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A297">
         <v>9</v>
       </c>
@@ -7295,8 +8172,11 @@
       <c r="G297">
         <v>19.059999999999999</v>
       </c>
-    </row>
-    <row r="298" spans="1:7">
+      <c r="H297">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A298">
         <v>9</v>
       </c>
@@ -7318,8 +8198,11 @@
       <c r="G298">
         <v>26.57</v>
       </c>
-    </row>
-    <row r="299" spans="1:7">
+      <c r="H298">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A299">
         <v>9</v>
       </c>
@@ -7341,8 +8224,11 @@
       <c r="G299">
         <v>34.33</v>
       </c>
-    </row>
-    <row r="300" spans="1:7">
+      <c r="H299">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A300">
         <v>9</v>
       </c>
@@ -7364,8 +8250,11 @@
       <c r="G300">
         <v>26.18</v>
       </c>
-    </row>
-    <row r="301" spans="1:7">
+      <c r="H300">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A301">
         <v>9</v>
       </c>
@@ -7387,8 +8276,11 @@
       <c r="G301">
         <v>28.98</v>
       </c>
-    </row>
-    <row r="302" spans="1:7">
+      <c r="H301">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A302">
         <v>9</v>
       </c>
@@ -7410,8 +8302,11 @@
       <c r="G302">
         <v>26.42</v>
       </c>
-    </row>
-    <row r="303" spans="1:7">
+      <c r="H302">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A303">
         <v>9</v>
       </c>
@@ -7433,8 +8328,11 @@
       <c r="G303">
         <v>23.5</v>
       </c>
-    </row>
-    <row r="304" spans="1:7">
+      <c r="H303">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A304">
         <v>9</v>
       </c>
@@ -7456,8 +8354,11 @@
       <c r="G304">
         <v>25.56</v>
       </c>
-    </row>
-    <row r="305" spans="1:7">
+      <c r="H304">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A305">
         <v>9</v>
       </c>
@@ -7479,8 +8380,11 @@
       <c r="G305">
         <v>24.77</v>
       </c>
-    </row>
-    <row r="306" spans="1:7">
+      <c r="H305">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A306">
         <v>9</v>
       </c>
@@ -7502,8 +8406,11 @@
       <c r="G306">
         <v>37.909999999999997</v>
       </c>
-    </row>
-    <row r="307" spans="1:7">
+      <c r="H306">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A307">
         <v>9</v>
       </c>
@@ -7525,8 +8432,11 @@
       <c r="G307">
         <v>28.74</v>
       </c>
-    </row>
-    <row r="308" spans="1:7">
+      <c r="H307">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A308">
         <v>9</v>
       </c>
@@ -7548,8 +8458,11 @@
       <c r="G308">
         <v>27.38</v>
       </c>
-    </row>
-    <row r="309" spans="1:7">
+      <c r="H308">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A309">
         <v>9</v>
       </c>
@@ -7571,8 +8484,11 @@
       <c r="G309">
         <v>20.93</v>
       </c>
-    </row>
-    <row r="310" spans="1:7">
+      <c r="H309">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A310">
         <v>9</v>
       </c>
@@ -7594,8 +8510,11 @@
       <c r="G310">
         <v>25.83</v>
       </c>
-    </row>
-    <row r="311" spans="1:7">
+      <c r="H310">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A311">
         <v>9</v>
       </c>
@@ -7617,8 +8536,11 @@
       <c r="G311">
         <v>29.61</v>
       </c>
-    </row>
-    <row r="312" spans="1:7">
+      <c r="H311">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A312">
         <v>9</v>
       </c>
@@ -7640,8 +8562,11 @@
       <c r="G312">
         <v>20.41</v>
       </c>
-    </row>
-    <row r="313" spans="1:7">
+      <c r="H312">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A313">
         <v>9</v>
       </c>
@@ -7663,8 +8588,11 @@
       <c r="G313">
         <v>18.88</v>
       </c>
-    </row>
-    <row r="314" spans="1:7">
+      <c r="H313">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A314">
         <v>9</v>
       </c>
@@ -7686,8 +8614,11 @@
       <c r="G314">
         <v>38.04</v>
       </c>
-    </row>
-    <row r="315" spans="1:7">
+      <c r="H314">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A315">
         <v>9</v>
       </c>
@@ -7709,8 +8640,11 @@
       <c r="G315">
         <v>16.39</v>
       </c>
-    </row>
-    <row r="316" spans="1:7">
+      <c r="H315">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A316">
         <v>9</v>
       </c>
@@ -7732,8 +8666,11 @@
       <c r="G316">
         <v>21.72</v>
       </c>
-    </row>
-    <row r="317" spans="1:7">
+      <c r="H316">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A317">
         <v>9</v>
       </c>
@@ -7755,8 +8692,11 @@
       <c r="G317">
         <v>23.34</v>
       </c>
-    </row>
-    <row r="318" spans="1:7">
+      <c r="H317">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A318">
         <v>9</v>
       </c>
@@ -7778,8 +8718,11 @@
       <c r="G318">
         <v>29.52</v>
       </c>
-    </row>
-    <row r="319" spans="1:7">
+      <c r="H318">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A319">
         <v>9</v>
       </c>
@@ -7801,8 +8744,11 @@
       <c r="G319">
         <v>22.56</v>
       </c>
-    </row>
-    <row r="320" spans="1:7">
+      <c r="H319">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A320">
         <v>9</v>
       </c>
@@ -7824,8 +8770,11 @@
       <c r="G320">
         <v>25.57</v>
       </c>
-    </row>
-    <row r="321" spans="1:7">
+      <c r="H320">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A321">
         <v>9</v>
       </c>
@@ -7847,8 +8796,11 @@
       <c r="G321">
         <v>18.260000000000002</v>
       </c>
-    </row>
-    <row r="322" spans="1:7">
+      <c r="H321">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A322">
         <v>9</v>
       </c>
@@ -7870,8 +8822,11 @@
       <c r="G322">
         <v>31.92</v>
       </c>
-    </row>
-    <row r="323" spans="1:7">
+      <c r="H322">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A323">
         <v>9</v>
       </c>
@@ -7893,8 +8848,11 @@
       <c r="G323">
         <v>22.52</v>
       </c>
-    </row>
-    <row r="324" spans="1:7">
+      <c r="H323">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A324">
         <v>9</v>
       </c>
@@ -7916,8 +8874,11 @@
       <c r="G324">
         <v>25.38</v>
       </c>
-    </row>
-    <row r="325" spans="1:7">
+      <c r="H324">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A325">
         <v>9</v>
       </c>
@@ -7939,8 +8900,11 @@
       <c r="G325">
         <v>24.47</v>
       </c>
-    </row>
-    <row r="326" spans="1:7">
+      <c r="H325">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A326">
         <v>9</v>
       </c>
@@ -7962,8 +8926,11 @@
       <c r="G326">
         <v>26.04</v>
       </c>
-    </row>
-    <row r="327" spans="1:7">
+      <c r="H326">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A327">
         <v>9</v>
       </c>
@@ -7985,8 +8952,11 @@
       <c r="G327">
         <v>21.19</v>
       </c>
-    </row>
-    <row r="328" spans="1:7">
+      <c r="H327">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A328">
         <v>9</v>
       </c>
@@ -8008,8 +8978,11 @@
       <c r="G328">
         <v>31.47</v>
       </c>
-    </row>
-    <row r="329" spans="1:7">
+      <c r="H328">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A329">
         <v>9</v>
       </c>
@@ -8031,8 +9004,11 @@
       <c r="G329">
         <v>30.03</v>
       </c>
-    </row>
-    <row r="330" spans="1:7">
+      <c r="H329">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A330">
         <v>9</v>
       </c>
@@ -8054,8 +9030,11 @@
       <c r="G330">
         <v>23.81</v>
       </c>
-    </row>
-    <row r="331" spans="1:7">
+      <c r="H330">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A331">
         <v>9</v>
       </c>
@@ -8077,8 +9056,11 @@
       <c r="G331">
         <v>24.06</v>
       </c>
-    </row>
-    <row r="332" spans="1:7">
+      <c r="H331">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A332">
         <v>9</v>
       </c>
@@ -8100,8 +9082,11 @@
       <c r="G332">
         <v>33.6</v>
       </c>
-    </row>
-    <row r="333" spans="1:7">
+      <c r="H332">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A333">
         <v>9</v>
       </c>
@@ -8123,8 +9108,11 @@
       <c r="G333">
         <v>35.29</v>
       </c>
-    </row>
-    <row r="334" spans="1:7">
+      <c r="H333">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A334">
         <v>9</v>
       </c>
@@ -8146,8 +9134,11 @@
       <c r="G334">
         <v>21.2</v>
       </c>
-    </row>
-    <row r="335" spans="1:7">
+      <c r="H334">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A335">
         <v>9</v>
       </c>
@@ -8169,8 +9160,11 @@
       <c r="G335">
         <v>20.13</v>
       </c>
-    </row>
-    <row r="336" spans="1:7">
+      <c r="H335">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A336">
         <v>9</v>
       </c>
@@ -8192,8 +9186,11 @@
       <c r="G336">
         <v>29.91</v>
       </c>
-    </row>
-    <row r="337" spans="1:7">
+      <c r="H336">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A337">
         <v>9</v>
       </c>
@@ -8215,8 +9212,11 @@
       <c r="G337">
         <v>34.24</v>
       </c>
-    </row>
-    <row r="338" spans="1:7">
+      <c r="H337">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A338">
         <v>9</v>
       </c>
@@ -8238,8 +9238,11 @@
       <c r="G338">
         <v>25.22</v>
       </c>
-    </row>
-    <row r="339" spans="1:7">
+      <c r="H338">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A339">
         <v>9</v>
       </c>
@@ -8261,8 +9264,11 @@
       <c r="G339">
         <v>21.13</v>
       </c>
-    </row>
-    <row r="340" spans="1:7">
+      <c r="H339">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A340">
         <v>9</v>
       </c>
@@ -8284,8 +9290,11 @@
       <c r="G340">
         <v>39.21</v>
       </c>
-    </row>
-    <row r="341" spans="1:7">
+      <c r="H340">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A341">
         <v>9</v>
       </c>
@@ -8307,8 +9316,11 @@
       <c r="G341">
         <v>28.3</v>
       </c>
-    </row>
-    <row r="342" spans="1:7">
+      <c r="H341">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A342">
         <v>9</v>
       </c>
@@ -8330,8 +9342,11 @@
       <c r="G342">
         <v>22.15</v>
       </c>
-    </row>
-    <row r="343" spans="1:7">
+      <c r="H342">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A343">
         <v>9</v>
       </c>
@@ -8353,8 +9368,11 @@
       <c r="G343">
         <v>14.07</v>
       </c>
-    </row>
-    <row r="344" spans="1:7">
+      <c r="H343">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A344">
         <v>9</v>
       </c>
@@ -8376,8 +9394,11 @@
       <c r="G344">
         <v>18.32</v>
       </c>
-    </row>
-    <row r="345" spans="1:7">
+      <c r="H344">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A345">
         <v>9</v>
       </c>
@@ -8399,8 +9420,11 @@
       <c r="G345">
         <v>20.66</v>
       </c>
-    </row>
-    <row r="346" spans="1:7">
+      <c r="H345">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A346">
         <v>9</v>
       </c>
@@ -8422,8 +9446,11 @@
       <c r="G346">
         <v>21.19</v>
       </c>
-    </row>
-    <row r="347" spans="1:7">
+      <c r="H346">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A347">
         <v>9</v>
       </c>
@@ -8445,8 +9472,11 @@
       <c r="G347">
         <v>18.100000000000001</v>
       </c>
-    </row>
-    <row r="348" spans="1:7">
+      <c r="H347">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A348">
         <v>9</v>
       </c>
@@ -8468,8 +9498,11 @@
       <c r="G348">
         <v>28.3</v>
       </c>
-    </row>
-    <row r="349" spans="1:7">
+      <c r="H348">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A349">
         <v>9</v>
       </c>
@@ -8491,8 +9524,11 @@
       <c r="G349">
         <v>20.69</v>
       </c>
-    </row>
-    <row r="350" spans="1:7" ht="15">
+      <c r="H349">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A350">
         <v>9</v>
       </c>
@@ -8514,8 +9550,11 @@
       <c r="G350" s="1">
         <v>29.45</v>
       </c>
-    </row>
-    <row r="351" spans="1:7">
+      <c r="H350">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A351">
         <v>9</v>
       </c>
@@ -8536,6 +9575,9 @@
       </c>
       <c r="G351">
         <v>21.51</v>
+      </c>
+      <c r="H351">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
